--- a/Config/Excels/Local/L-Localization-设置.xlsx
+++ b/Config/Excels/Local/L-Localization-设置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24645" windowHeight="11610"/>
+    <workbookView windowHeight="18450"/>
   </bookViews>
   <sheets>
     <sheet name="ui" sheetId="11" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113">
   <si>
     <t>##var</t>
   </si>
@@ -25,6 +25,9 @@
     <t>key</t>
   </si>
   <si>
+    <t>is_code</t>
+  </si>
+  <si>
     <t>ChineseSimplified</t>
   </si>
   <si>
@@ -73,10 +76,16 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>是否导出到代码中</t>
   </si>
   <si>
     <t>简体中文</t>
@@ -351,8 +360,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -373,13 +382,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -394,6 +396,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -401,10 +457,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -416,9 +489,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -431,17 +503,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -456,61 +519,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -531,19 +540,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,37 +678,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -597,115 +714,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -730,21 +739,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -782,6 +776,50 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -802,45 +840,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -849,137 +858,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -990,10 +999,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1315,425 +1330,450 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8.66666666666667" style="2"/>
     <col min="2" max="2" width="15.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="22" style="3" customWidth="1"/>
-    <col min="4" max="5" width="15.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.875" style="3" customWidth="1"/>
-    <col min="7" max="8" width="15.75" style="3" customWidth="1"/>
-    <col min="9" max="9" width="20.625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="24" style="3" customWidth="1"/>
-    <col min="11" max="11" width="22.625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="19.75" style="3" customWidth="1"/>
-    <col min="13" max="13" width="26" style="3" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="3" customWidth="1"/>
-    <col min="15" max="15" width="23.75" style="3" customWidth="1"/>
-    <col min="16" max="16" width="23.375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="18.375" style="3" customWidth="1"/>
-    <col min="18" max="16384" width="8.66666666666667" style="4"/>
+    <col min="4" max="4" width="15" style="4" customWidth="1"/>
+    <col min="5" max="6" width="15.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.875" style="3" customWidth="1"/>
+    <col min="8" max="9" width="15.75" style="3" customWidth="1"/>
+    <col min="10" max="10" width="20.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24" style="3" customWidth="1"/>
+    <col min="12" max="12" width="22.625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="19.75" style="3" customWidth="1"/>
+    <col min="14" max="14" width="26" style="3" customWidth="1"/>
+    <col min="15" max="15" width="21.25" style="3" customWidth="1"/>
+    <col min="16" max="16" width="23.75" style="3" customWidth="1"/>
+    <col min="17" max="17" width="23.375" style="3" customWidth="1"/>
+    <col min="18" max="18" width="18.375" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.66666666666667" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:18">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
-      <c r="A2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:18">
+      <c r="A2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>18</v>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
-      <c r="A3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:18">
+      <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="N3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="O3" s="6" t="s">
         <v>34</v>
       </c>
+      <c r="P3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" ht="15" spans="1:17">
+    <row r="4" ht="15" spans="1:18">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="D4" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:17">
+    <row r="5" ht="15" spans="1:18">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="D5" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:17">
+    <row r="6" ht="15" spans="1:18">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="D6" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:17">
+    <row r="7" ht="15" spans="1:18">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="D7" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="8" ht="15" spans="1:17">
+    <row r="8" ht="15" spans="1:18">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
+      </c>
+      <c r="D8" s="7" t="b">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
